--- a/results/Int Task Remove ACC -0.9/Linea_fi_all.xlsx
+++ b/results/Int Task Remove ACC -0.9/Linea_fi_all.xlsx
@@ -926,7 +926,7 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.014486552567237087 +/- 0.0023243463743070265</t>
+          <t>0.014455990220048832 +/- 0.0023277596606759827</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.0221468593335299 +/- 0.0034173860882064475</t>
+          <t>0.02217634915953993 +/- 0.0034233610996004713</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1386,7 +1386,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.010498378059569402 +/- 0.0025749194872241982</t>
+          <t>0.01046888823355937 +/- 0.002568325139463646</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0018644569399230537 +/- 0.0027254319313034315</t>
+          <t>0.001834862385321101 +/- 0.0027020330773633383</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.0004735128736312433 +/- 0.0007028317305142174</t>
+          <t>-0.0005327019828351487 +/- 0.000697829305862763</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1811,7 +1811,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>-0.0037289138798461074 +/- 0.005966367901655453</t>
+          <t>-0.0037585084344480602 +/- 0.005923422370632303</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>-0.0014501331754956826 +/- 0.0015573035947821995</t>
+          <t>-0.0014501331754956826 +/- 0.0016607265873451252</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-0.0004735128736312433 +/- 0.0007028317305142174</t>
+          <t>-0.0004735128736312433 +/- 0.0006902576969334353</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.029357798165137616 +/- 0.0036385659400541563</t>
+          <t>0.02938739271973957 +/- 0.0036028863415054095</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -2246,74 +2246,74 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
+          <t>-8.862629246676468e-05 +/- 0.0008041747467542764</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.01722304283604136 +/- 0.002824477903134498</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.03716395864106351 +/- 0.0030638445287950954</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.03716395864106351 +/- 0.0030638445287950954</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.030339734121122564 +/- 0.00418216363111068</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.026351550960118143 +/- 0.004585786212568899</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>0.007474150664697155 +/- 0.002414693776888548</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>-0.01477104874446089 +/- 0.0031320196822921128</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>0.0061447562776956845 +/- 0.0028050995498893135</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0.0016543574593796072 +/- 0.002454662106687253</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0.27474150664697194 +/- 0.006777964147568677</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>0.01893648449039883 +/- 0.002656982810256695</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>0.13559822747415065 +/- 0.00674181474769674</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
           <t>-0.0001477104874446078 +/- 0.0008277060990323088</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>0.01722304283604136 +/- 0.002824477903134498</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0.03716395864106351 +/- 0.0030638445287950954</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>0.03716395864106351 +/- 0.0030638445287950954</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>0.030339734121122564 +/- 0.00418216363111068</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0.026351550960118143 +/- 0.004585786212568899</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>0.007474150664697155 +/- 0.002414693776888548</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>-0.01477104874446089 +/- 0.0031320196822921128</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>0.0061447562776956845 +/- 0.0028050995498893135</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>0.0016543574593796072 +/- 0.002454662106687253</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0.27474150664697194 +/- 0.006777964147568677</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>0.01893648449039883 +/- 0.002656982810256695</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>0.13559822747415065 +/- 0.00674181474769674</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>-0.0001477104874446078 +/- 0.0008277060990323088</t>
-        </is>
-      </c>
       <c r="W5" t="inlineStr">
         <is>
           <t>0.01279172821270308 +/- 0.00523662323458703</t>
@@ -2496,7 +2496,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-0.00833087149187598 +/- 0.0014520774862563758</t>
+          <t>-0.008360413589364901 +/- 0.001447562776957173</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.04218472468916521 +/- 0.0030341593326715832</t>
+          <t>0.04212551805802254 +/- 0.0029987150449135446</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -3421,7 +3421,7 @@
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>0.025227201504230655 +/- 0.003087244074015737</t>
+          <t>0.025195863365716088 +/- 0.003022790486189269</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.07822152886115447 +/- 0.0052005096116385695</t>
+          <t>0.07815912636505461 +/- 0.00518025292420096</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3586,7 +3586,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.10695787831513259 +/- 0.006093117253658224</t>
+          <t>0.1069266770670827 +/- 0.006059873591642024</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.09419656786271453 +/- 0.004251735352930298</t>
+          <t>0.09425897035881436 +/- 0.004258598899186173</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.00071762870514821 +/- 0.0008719618478927984</t>
+          <t>0.0007488299531981379 +/- 0.0008278626621791851</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -4006,7 +4006,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.013999410551134716 +/- 0.0020892199939224454</t>
+          <t>0.014058355437665804 +/- 0.0019991356182860673</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>0.016651930445033925 +/- 0.0029802163890593424</t>
+          <t>0.016681402888299467 +/- 0.002982984009167109</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4271,7 +4271,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-0.0318302387267904 +/- 0.005283711259426802</t>
+          <t>-0.031800766283524864 +/- 0.005286094474698948</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>-0.02452107279693483 +/- 0.0029789045136441464</t>
+          <t>-0.024491600353669284 +/- 0.002995334157730999</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4801,72 +4801,72 @@
       </c>
       <c r="BW10" t="inlineStr">
         <is>
+          <t>0.04281186977816197 +/- 0.0027368117745982094</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>0.0 +/- 0.0</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>-0.0004321521175453147 +/- 0.0006344775438071024</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>-0.0004321521175453147 +/- 0.0006344775438071024</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>0.0018438490348603232 +/- 0.0008270066317722478</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>0.0015845577643330943 +/- 0.00023227478387491588</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>0.004984154422356735 +/- 0.0006448582335234801</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>-0.004753673292999083 +/- 0.0005797929068711492</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>0.0020167098818784867 +/- 0.001249177953827647</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>-0.0003745318352059268 +/- 0.001804030216589248</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
+          <t>0.009651397291846785 +/- 0.0023414333360159928</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
+          <t>-0.0002016709881878076 +/- 0.00025929127052721644</t>
+        </is>
+      </c>
+      <c r="CI10" t="inlineStr">
+        <is>
+          <t>0.0625756266205705 +/- 0.0036437710754854296</t>
+        </is>
+      </c>
+      <c r="CJ10" t="inlineStr">
+        <is>
           <t>0.042783059636992284 +/- 0.002770121666162239</t>
-        </is>
-      </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>-0.0004321521175453147 +/- 0.0006344775438071024</t>
-        </is>
-      </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>-0.0004321521175453147 +/- 0.0006344775438071024</t>
-        </is>
-      </c>
-      <c r="CA10" t="inlineStr">
-        <is>
-          <t>0.0018438490348603232 +/- 0.0008270066317722478</t>
-        </is>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>0.0015845577643330943 +/- 0.00023227478387491588</t>
-        </is>
-      </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>0.004984154422356735 +/- 0.0006448582335234801</t>
-        </is>
-      </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>-0.004753673292999083 +/- 0.0005797929068711492</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>0.0020167098818784867 +/- 0.001249177953827647</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>-0.0003745318352059268 +/- 0.001804030216589248</t>
-        </is>
-      </c>
-      <c r="CG10" t="inlineStr">
-        <is>
-          <t>0.009651397291846785 +/- 0.0023414333360159928</t>
-        </is>
-      </c>
-      <c r="CH10" t="inlineStr">
-        <is>
-          <t>-0.0002016709881878076 +/- 0.00025929127052721644</t>
-        </is>
-      </c>
-      <c r="CI10" t="inlineStr">
-        <is>
-          <t>0.0625756266205705 +/- 0.0036437710754854296</t>
-        </is>
-      </c>
-      <c r="CJ10" t="inlineStr">
-        <is>
-          <t>0.04281186977816197 +/- 0.0027368117745982094</t>
         </is>
       </c>
       <c r="CK10" t="inlineStr">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.09289113622843544 +/- 0.0032854889014400997</t>
+          <t>0.09286139202855441 +/- 0.003359383201307658</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.0011600237953599325 +/- 0.001306376636287792</t>
+          <t>-0.0012195121951219744 +/- 0.0013198517389847587</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.000832837596668623 +/- 0.0016603552334268714</t>
+          <t>0.000832837596668623 +/- 0.0016171656417689705</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -4941,12 +4941,12 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>0.14137418203450328 +/- 0.004028225703778093</t>
+          <t>0.1414039262343843 +/- 0.004017559549054867</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>0.025639500297441976 +/- 0.0024914207723226683</t>
+          <t>0.025669244497322996 +/- 0.002517034265085082</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -4981,7 +4981,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>0.000832837596668623 +/- 0.0016496638457896534</t>
+          <t>0.000862581796549644 +/- 0.0016261673923660509</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -5136,7 +5136,7 @@
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>0.007257584770969638 +/- 0.002300901797241383</t>
+          <t>0.0072873289708506594 +/- 0.0023354406296792005</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
